--- a/data/trans_orig/IP07A20-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07A20-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2007 (tasa de respuesta: 99,0%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2007 (tasa de respuesta: 99,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>20279</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13573</t>
+          <t>13649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20092</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,45%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>10540</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26468</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36177</t>
+          <t>36192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27571</t>
+          <t>27079</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39341</t>
+          <t>39452</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58212</t>
+          <t>57388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74069</t>
+          <t>73439</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>14867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12575</t>
+          <t>12591</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24100</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19978</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35097</t>
+          <t>36137</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>19542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30072</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>47,25%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20845</t>
+          <t>20385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25972</t>
+          <t>25487</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38349</t>
+          <t>38474</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,8%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20354</t>
+          <t>20377</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23113</t>
+          <t>23263</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37402</t>
+          <t>36819</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,39%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>24380</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>11251</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>21950</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>28938</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42203</t>
+          <t>43078</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16359</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>14020</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>24217</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,13%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11208</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>20783</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>49,03%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12297</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14254</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11875</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23450</t>
+          <t>24095</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20043</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>23357</t>
+          <t>22861</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35498</t>
+          <t>35088</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,39%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>13787</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>21420</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>33650</t>
+          <t>33870</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>22980</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>36156</t>
+          <t>35902</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>53868</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>19668</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>31587</t>
+          <t>31718</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>29552</t>
+          <t>29989</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>41975</t>
+          <t>42009</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>52168</t>
+          <t>51471</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>69484</t>
+          <t>69968</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,75%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>17512</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>21671</t>
+          <t>22195</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>35418</t>
+          <t>35666</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>19589</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>32172</t>
+          <t>32932</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>44367</t>
+          <t>46058</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>63229</t>
+          <t>63854</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>30502</t>
+          <t>31208</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>44990</t>
+          <t>44763</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>28890</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>42882</t>
+          <t>42422</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>64491</t>
+          <t>64110</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>83487</t>
+          <t>82806</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>20268</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>130357</t>
+          <t>128755</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>157741</t>
+          <t>158587</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>112237</t>
+          <t>113696</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>141656</t>
+          <t>142355</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>250338</t>
+          <t>248371</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>292281</t>
+          <t>290182</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,82%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>124910</t>
+          <t>125097</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>152441</t>
+          <t>154385</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>145249</t>
+          <t>146029</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>175793</t>
+          <t>175146</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>278823</t>
+          <t>280819</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>320449</t>
+          <t>320318</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,38%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19229</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>34758</t>
+          <t>35781</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>55043</t>
+          <t>55196</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>59229</t>
+          <t>60014</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>84981</t>
+          <t>85292</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>23038</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6655,39 +6655,39 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>4175</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>4162</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20930</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26674</t>
+          <t>26577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34890</t>
+          <t>35461</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45109</t>
+          <t>46146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27669</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38036</t>
+          <t>38023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31110</t>
+          <t>30843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41787</t>
+          <t>41638</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62669</t>
+          <t>61933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76986</t>
+          <t>77222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,08%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15113</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16641</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>14843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>28108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18180</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24211</t>
+          <t>24105</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20891</t>
+          <t>21453</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28461</t>
+          <t>28852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>42135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>52003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21279</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>11155</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21189</t>
+          <t>21170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24138</t>
+          <t>24808</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38539</t>
+          <t>39084</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>16829</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26837</t>
+          <t>26630</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12022</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31847</t>
+          <t>30831</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46715</t>
+          <t>45638</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>431</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15121</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18387</t>
+          <t>17512</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28836</t>
+          <t>28335</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16587</t>
+          <t>17814</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8565</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>19026</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>27417</t>
+          <t>27723</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32501</t>
+          <t>32232</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>43975</t>
+          <t>44065</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,69%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>14826</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>30198</t>
+          <t>30717</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>42576</t>
+          <t>42441</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>30914</t>
+          <t>30907</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>42530</t>
+          <t>41804</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>64848</t>
+          <t>64817</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>80985</t>
+          <t>81687</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>11948</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>23694</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>19794</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>24082</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>39731</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>23015</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>35805</t>
+          <t>36655</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>20706</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>34397</t>
+          <t>34758</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>46876</t>
+          <t>47613</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>65756</t>
+          <t>67096</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>33189</t>
+          <t>33191</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>47740</t>
+          <t>48028</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>33844</t>
+          <t>33555</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>47981</t>
+          <t>49203</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>71948</t>
+          <t>71074</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>92066</t>
+          <t>91070</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -12337,7 +12337,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>175024</t>
+          <t>174466</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>203519</t>
+          <t>204506</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>176634</t>
+          <t>177438</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>205886</t>
+          <t>206376</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>358713</t>
+          <t>362196</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>402789</t>
+          <t>401932</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>92578</t>
+          <t>92885</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>121803</t>
+          <t>122301</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>95099</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>124089</t>
+          <t>124125</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>196080</t>
+          <t>196475</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>236945</t>
+          <t>233712</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>28272</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>28972</t>
+          <t>28313</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>30149</t>
+          <t>30710</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>51591</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>16144</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2016 (tasa de respuesta: 98,52%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2016 (tasa de respuesta: 98,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>18733</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25918</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23040</t>
+          <t>22749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34526</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46872</t>
+          <t>46892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>16773</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28248</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39866</t>
+          <t>39829</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45325</t>
+          <t>45592</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65538</t>
+          <t>64206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81867</t>
+          <t>82279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>20502</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18947</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>21065</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36247</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>11608</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18796</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29041</t>
+          <t>29410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16012</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25661</t>
+          <t>25577</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38067</t>
+          <t>39301</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51669</t>
+          <t>52282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>75,16%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14543</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12575</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25226</t>
+          <t>25113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>828</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -15223,7 +15223,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24898</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>34291</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27594</t>
+          <t>28410</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37876</t>
+          <t>37488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56194</t>
+          <t>56202</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69254</t>
+          <t>68867</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>9886</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>978</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7701</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9811</t>
+          <t>9379</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22396</t>
+          <t>22572</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>26497</t>
+          <t>27789</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36554</t>
+          <t>37147</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>83,43%</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -16665,7 +16665,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21019</t>
+          <t>20938</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18967</t>
+          <t>19624</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24230</t>
+          <t>24352</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37402</t>
+          <t>37000</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,26%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16345</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>14498</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27636</t>
+          <t>27631</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,0%</t>
         </is>
       </c>
     </row>
@@ -17116,12 +17116,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>692</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17131,12 +17131,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>9574</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17166,12 +17166,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17362,7 +17362,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>18028</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>31477</t>
+          <t>30953</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>39234</t>
+          <t>39815</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>58546</t>
+          <t>58373</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>28755</t>
+          <t>27723</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>42186</t>
+          <t>41478</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>37362</t>
+          <t>37647</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>55570</t>
+          <t>55779</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>75054</t>
+          <t>74845</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,87%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>14448</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>23447</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>25274</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>38986</t>
+          <t>39242</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>24433</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>38843</t>
+          <t>38595</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>54172</t>
+          <t>53432</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>74224</t>
+          <t>73377</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>30317</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>45417</t>
+          <t>44752</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>28751</t>
+          <t>29159</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>43240</t>
+          <t>43362</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>63315</t>
+          <t>63797</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>82992</t>
+          <t>84087</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>54,06%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>16941</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>24137</t>
+          <t>24340</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -18746,7 +18746,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18761,7 +18761,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>172509</t>
+          <t>172687</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>205403</t>
+          <t>204699</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>173476</t>
+          <t>173853</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>203966</t>
+          <t>204992</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>356455</t>
+          <t>354578</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>400078</t>
+          <t>402416</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>118373</t>
+          <t>116979</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>148833</t>
+          <t>148668</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>116070</t>
+          <t>116458</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>147393</t>
+          <t>146823</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>243987</t>
+          <t>244320</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>286054</t>
+          <t>288686</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>23636</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>40761</t>
+          <t>39371</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>21012</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>40641</t>
+          <t>38879</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>49672</t>
+          <t>49835</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>74192</t>
+          <t>72745</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -19280,7 +19280,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
